--- a/Result/profitability/1809.xlsx
+++ b/Result/profitability/1809.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06875000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="N2" t="n">
-        <v>20.2025</v>
+        <v>20.24125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0825</v>
+        <v>0.08</v>
       </c>
       <c r="N3" t="n">
-        <v>20.11</v>
+        <v>20.225</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09625</v>
+        <v>0.095</v>
       </c>
       <c r="N4" t="n">
-        <v>20.455</v>
+        <v>20.615</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1021,7 +1021,7 @@
         <v>0.1075</v>
       </c>
       <c r="N5" t="n">
-        <v>20.13875</v>
+        <v>20.36</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09875</v>
+        <v>0.1</v>
       </c>
       <c r="N6" t="n">
-        <v>19.85</v>
+        <v>20.17875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.15875</v>
+        <v>0.15375</v>
       </c>
       <c r="N7" t="n">
-        <v>20.54</v>
+        <v>20.53125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.235</v>
+        <v>0.23375</v>
       </c>
       <c r="N8" t="n">
-        <v>20.54375</v>
+        <v>20.78625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>610</v>
+      </c>
+      <c r="D75" t="n">
+        <v>480</v>
+      </c>
+      <c r="E75" t="n">
+        <v>130</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.2125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2000000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.939999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1001548786783686</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09058341862845443</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
